--- a/03_Outputs/De_la_Paz/09_Salud/salud.xlsx
+++ b/03_Outputs/De_la_Paz/09_Salud/salud.xlsx
@@ -909,7 +909,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="11">
-        <v>47.4850391143436</v>
+        <v>47.4850391143435</v>
       </c>
     </row>
   </sheetData>
